--- a/capacity-planner.xlsx
+++ b/capacity-planner.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://capgemini-my.sharepoint.com/personal/nicketa_nicketa_capgemini_com/Documents/Work/2. POC/Specathon/Scrum-Master/Scrum-Master/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="11_F25DC773A252ABDACC104886619B6F9A5BDE58E9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F43A87BF-BF02-433F-A72B-41502E5ADBE2}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="11_F25DC773A252ABDACC104886619B6F9A5BDE58E9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7145C81-D2D9-48FB-BD08-6F0376278B97}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Name</t>
   </si>
@@ -51,6 +51,18 @@
   </si>
   <si>
     <t>Capacity gap</t>
+  </si>
+  <si>
+    <t>Sprint 1</t>
+  </si>
+  <si>
+    <t>John</t>
+  </si>
+  <si>
+    <t>Sprint 2</t>
+  </si>
+  <si>
+    <t>Neha</t>
   </si>
 </sst>
 </file>
@@ -389,15 +401,39 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2">
+        <v>40</v>
+      </c>
+      <c r="D2">
+        <v>35</v>
+      </c>
       <c r="E2">
         <f>C2-D2</f>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3">
+        <v>40</v>
+      </c>
+      <c r="D3">
+        <v>45</v>
+      </c>
       <c r="E3">
         <f t="shared" ref="E3:E66" si="0">C3-D3</f>
-        <v>0</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
